--- a/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N43_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N43_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>13.20071091775234</v>
+        <v>2.145115524134756</v>
       </c>
       <c r="D2" t="n">
-        <v>17.05110046790919</v>
+        <v>2.770803826035243</v>
       </c>
       <c r="E2" t="n">
-        <v>14.08832957226955</v>
+        <v>2.289353555493801</v>
       </c>
       <c r="F2" t="n">
-        <v>13.46873289731883</v>
+        <v>2.18866909581431</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>50.57554468354354</v>
+        <v>8.218526011075825</v>
       </c>
       <c r="D3" t="n">
-        <v>50.33404653541889</v>
+        <v>8.17928256200557</v>
       </c>
       <c r="E3" t="n">
-        <v>14.08832957226955</v>
+        <v>2.289353555493801</v>
       </c>
       <c r="F3" t="n">
-        <v>13.46873289731883</v>
+        <v>2.18866909581431</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>8.055822500108599</v>
+        <v>1.309071156267647</v>
       </c>
       <c r="D4" t="n">
-        <v>8.003198440914899</v>
+        <v>1.300519746648671</v>
       </c>
       <c r="E4" t="n">
-        <v>14.08832957226955</v>
+        <v>2.289353555493801</v>
       </c>
       <c r="F4" t="n">
-        <v>13.46873289731883</v>
+        <v>2.18866909581431</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>35.43882279622584</v>
+        <v>5.758808704386698</v>
       </c>
       <c r="D5" t="n">
-        <v>19.44799550152399</v>
+        <v>3.160299268997648</v>
       </c>
       <c r="E5" t="n">
-        <v>14.08832957226955</v>
+        <v>2.289353555493801</v>
       </c>
       <c r="F5" t="n">
-        <v>13.46873289731883</v>
+        <v>2.18866909581431</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>22.68171585234754</v>
+        <v>3.685778826006476</v>
       </c>
       <c r="D6" t="n">
-        <v>20.99006335881062</v>
+        <v>3.410885295806726</v>
       </c>
       <c r="E6" t="n">
-        <v>14.08832957226955</v>
+        <v>2.289353555493801</v>
       </c>
       <c r="F6" t="n">
-        <v>13.46873289731883</v>
+        <v>2.18866909581431</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>24.88877524379029</v>
+        <v>4.044425977115922</v>
       </c>
       <c r="D7" t="n">
-        <v>14.36911987561429</v>
+        <v>2.334981979787321</v>
       </c>
       <c r="E7" t="n">
-        <v>14.08832957226955</v>
+        <v>2.289353555493801</v>
       </c>
       <c r="F7" t="n">
-        <v>13.46873289731883</v>
+        <v>2.18866909581431</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
